--- a/docentes/Cruz Alejo José Armando - Estadisticos 20222.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20222.xlsx
@@ -559,16 +559,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -582,16 +585,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -656,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,7 +688,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20222.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20222.xlsx
@@ -662,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -688,7 +688,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
